--- a/06_ai-incident-response-playbook-simulation/exercises/solution/incident_response_solution.xlsx
+++ b/06_ai-incident-response-playbook-simulation/exercises/solution/incident_response_solution.xlsx
@@ -1182,128 +1182,44 @@
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"S1"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"S1"
 Reasoning: Deliberate manipulation of a safety-critical transit system poses immediate risk to passenger safety; classified as critical for rapid response.</t>
-          </r>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Anomaly detection algorithms, ML model behavior analysis, unusual request pattern analysis, behavioral fingerprinting"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Anomaly detection algorithms, ML model behavior analysis, unusual request pattern analysis, behavioral fingerprinting"
 Reasoning: Combined detection methods help identify coordinated attack signatures across the system; behavioral analysis reveals non-organic request patterns.</t>
-          </r>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Rate limiting and request throttling; isolate affected routing service; notify security team; preserve logs for investigation"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Rate limiting and request throttling; isolate affected routing service; notify security team; preserve logs for investigation"
 Reasoning: Immediate isolation prevents cascading failures; rate limiting stops attack propagation; preserving logs enables forensic analysis and attribution.</t>
-          </r>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Analyze attack patterns and signatures; determine scope of affected routes; assess whether passenger safety was compromised; review attacker capabilities"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Analyze attack patterns and signatures; determine scope of affected routes; assess whether passenger safety was compromised; review attacker capabilities"
 Reasoning: Pattern analysis identifies attack sophistication; scope assessment helps quantify impact; safety review ensures no undetected harm occurred.</t>
-          </r>
         </is>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Implement input validation and adversarial robustness techniques; add intrusion detection; improve API authentication"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Implement input validation and adversarial robustness techniques; add intrusion detection; improve API authentication"
 Reasoning: Input validation blocks malformed requests; adversarial robustness hardens model; improved auth prevents credential-based attacks.</t>
-          </r>
         </is>
       </c>
       <c r="J9" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Security alert to ops; law enforcement notification for potential coordinated attacks; briefing to executive team and board"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Security alert to ops; law enforcement notification for potential coordinated attacks; briefing to executive team and board"
 Reasoning: Ops team needs immediate awareness; law enforcement may be necessary for prosecuting attackers; leadership needs to understand security posture impact.</t>
-          </r>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Adversarial testing against the routing engine; system hardening with cryptographic verification; threat modeling for supply chain attacks"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Adversarial testing against the routing engine; system hardening with cryptographic verification; threat modeling for supply chain attacks"
 Reasoning: Adversarial testing identifies similar vulnerabilities proactively; cryptographic verification prevents tampering; threat modeling improves long-term security posture.</t>
-          </r>
         </is>
       </c>
     </row>
@@ -1330,128 +1246,44 @@
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"S1"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"S1"
 Reasoning: Data poisoning undermines the integrity of all downstream models and decisions; threatens fundamental trust in the AI system.</t>
-          </r>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Data validation and statistical anomaly detection; performance baseline comparison; data lineage tracking; checksums on training data"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Data validation and statistical anomaly detection; performance baseline comparison; data lineage tracking; checksums on training data"
 Reasoning: Statistical anomalies reveal contamination; performance baselines show degradation; checksums and lineage enable identification of poisoned batches.</t>
-          </r>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Halt all retraining; isolate compromised data; preserve evidence chain; activate incident commander; notify Chief Data Officer"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Halt all retraining; isolate compromised data; preserve evidence chain; activate incident commander; notify Chief Data Officer"
 Reasoning: Stopping retraining prevents poisoned models from deployment; evidence preservation enables investigation; rapid escalation ensures proper oversight.</t>
-          </r>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Audit data pipeline end-to-end; identify contamination source and entry point; assess impact on existing trained models; review access logs"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Audit data pipeline end-to-end; identify contamination source and entry point; assess impact on existing trained models; review access logs"
 Reasoning: Pipeline audit reveals vulnerabilities; source identification prevents recurrence; impact assessment informs remediation scope; access logs identify insider threats.</t>
-          </r>
         </is>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Data cleaning and validation; integrity checks at ingestion points; verified retraining with clean historical data; implement cryptographic integrity checks"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Data cleaning and validation; integrity checks at ingestion points; verified retraining with clean historical data; implement cryptographic integrity checks"
 Reasoning: Cleaning removes bad data; validation prevents future poisoning; verified retraining with curated data restores model trustworthiness; cryptographic checks ensure data hasn't been tampered.</t>
-          </r>
         </is>
       </c>
       <c r="J10" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Data governance briefing to compliance and engineering; engineering team notification of process improvements; training for data handling"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Data governance briefing to compliance and engineering; engineering team notification of process improvements; training for data handling"
 Reasoning: Governance needs awareness of vulnerabilities; engineering learns from incident; training prevents similar mistakes; transparency builds organizational resilience.</t>
-          </r>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Implement data validation gates in pipeline; fingerprinting of training data; stricter access controls; automated anomaly detection on data distributions"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Implement data validation gates in pipeline; fingerprinting of training data; stricter access controls; automated anomaly detection on data distributions"
 Reasoning: Validation gates catch issues early; fingerprinting enables quick identification; access controls limit poisoning opportunities; automated monitoring provides continuous safety.</t>
-          </r>
         </is>
       </c>
     </row>
@@ -1478,128 +1310,44 @@
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"S1"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"S1"
 Reasoning: Unauthorized access to an AI system controlling transit can enable data theft, system manipulation, or safety-critical routing errors affecting millions.</t>
-          </r>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Failed login attempts and rate limiting triggers; unusual access locations or times; off-hours access patterns; anomalous API key usage; geo-velocity checks"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Failed login attempts and rate limiting triggers; unusual access locations or times; off-hours access patterns; anomalous API key usage; geo-velocity checks"
 Reasoning: Failed attempts indicate compromise attempts; unusual patterns reveal unauthorized access; geo-velocity violations catch credential sharing; API anomalies show misuse.</t>
-          </r>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Immediate credential revocation; forced password reset for affected users; enable MFA across all accounts; revoke all API keys; disable compromised sessions"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Immediate credential revocation; forced password reset for affected users; enable MFA across all accounts; revoke all API keys; disable compromised sessions"
 Reasoning: Revocation stops attackers immediately; forced resets prevent reuse; MFA makes future compromises harder; API key revocation blocks programmatic access; session termination logs out intruders.</t>
-          </r>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Comprehensive access log audit; determine scope of unauthorized actions; identify affected systems and data; assess attacker dwell time"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Comprehensive access log audit; determine scope of unauthorized actions; identify affected systems and data; assess attacker dwell time"
 Reasoning: Log audit reveals what attacker accessed; scope determines impact magnitude; dwell time assessment shows detection delay; comprehensive review prevents missing lateral movement.</t>
-          </r>
         </is>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Stronger authentication (MFA/FIDO2); secret management and rotation; access review and removal of dormant accounts; hardware security keys for critical roles"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Stronger authentication (MFA/FIDO2); secret management and rotation; access review and removal of dormant accounts; hardware security keys for critical roles"
 Reasoning: MFA/FIDO2 prevents credential-based attacks; secret management prevents exposure; account cleanup reduces attack surface; hardware keys protect the highest-privilege accounts.</t>
-          </r>
         </is>
       </c>
       <c r="J11" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Security briefing to all teams; notification to affected users; optional credit monitoring if personal data was accessed; regulatory notification if required"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Security briefing to all teams; notification to affected users; optional credit monitoring if personal data was accessed; regulatory notification if required"
 Reasoning: Team awareness improves future vigilance; user notification builds trust; credit monitoring addresses data breach concerns; regulatory notification meets compliance obligations.</t>
-          </r>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Credential rotation policy; enhanced audit logging; security awareness training; phishing simulations; regular access reviews"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Credential rotation policy; enhanced audit logging; security awareness training; phishing simulations; regular access reviews"
 Reasoning: Regular rotation limits exposure window; audit logging improves detection; training reduces human vulnerabilities; simulations identify at-risk employees; reviews prevent privilege creep.</t>
-          </r>
         </is>
       </c>
     </row>
@@ -2175,79 +1923,36 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Conduct blameless postmortem meeting; document lessons learned; identify systemic improvements"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Conduct blameless postmortem meeting; document lessons learned; identify systemic improvements"
 Reasoning: Blameless approach encourages honest analysis; systematic documentation ensures findings are actionable; this step transforms incident experience into organizational learning.</t>
-          </r>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Incident Commander, Engineering Lead, affected team members, Product Manager, Data Science Lead"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Incident Commander, Engineering Lead, affected team members, Product Manager, Data Science Lead"
 Reasoning: Incident Commander ensures process integrity; Engineering/Data Science provide technical insights; Product understands customer impact; diverse perspectives identify root causes.</t>
-          </r>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Within 48 hours of incident resolution"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Within 48 hours of incident resolution"
 Reasoning: Quick turnaround captures fresh memory and emotional context; within 48 hours ensures urgency without fatigue; too late and details are forgotten.</t>
-          </r>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Postmortem document with timeline, root cause, contributing factors, action items with owners and deadlines"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>Postmortem Report Template</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Zoom, Confluence, Jira</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>"Postmortem document with timeline, root cause, contributing factors, action items with owners and deadlines"
 Reasoning: Structured documentation ensures completeness; clear ownership and deadlines drive accountability; shared document enables transparency and organizational learning.</t>
-          </r>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>Zoom, Confluence, Jira</t>
         </is>
       </c>
     </row>
@@ -2259,79 +1964,36 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Update runbooks with new procedures; add incident patterns to knowledge base; document root causes and solutions; update monitoring thresholds"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Update runbooks with new procedures; add incident patterns to knowledge base; document root causes and solutions; update monitoring thresholds"
 Reasoning: Runbook updates improve response for similar future incidents; knowledge base prevents rediscovery; monitoring improvements provide earlier detection.</t>
-          </r>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Knowledge Manager, Technical Writer, and relevant technical teams who handled the incident"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Knowledge Manager, Technical Writer, and relevant technical teams who handled the incident"
 Reasoning: Knowledge Manager ensures quality and consistency; Technical Writers ensure clarity for future teams; involved technical teams capture accurate details.</t>
-          </r>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Within 5 business days of incident resolution"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Within 5 business days of incident resolution"
 Reasoning: 5-day window allows action items to be completed before documentation; reasonable timeline avoids documentation backlog; ensures knowledge is current.</t>
-          </r>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Updated runbooks in Confluence, new alerting rules in monitoring system, root cause article in knowledge base"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>Runbook / KB Update Template</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Confluence, GitHub Wiki</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>"Updated runbooks in Confluence, new alerting rules in monitoring system, root cause article in knowledge base"
 Reasoning: Confluence ensures team can find procedures; updated alerts prevent recurrence; knowledge base article enables transfer of learning across organization.</t>
-          </r>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>Confluence, GitHub Wiki</t>
         </is>
       </c>
     </row>
@@ -2580,56 +2242,20 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Evaluate timeliness, accuracy, and clarity of customer and stakeholder communications throughout incident lifecycle"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Evaluate timeliness, accuracy, and clarity of customer and stakeholder communications throughout incident lifecycle"
 Reasoning: Timeliness assessment shows if notifications met SLAs; accuracy review catches misleading information; clarity ensures diverse audiences understood impact.</t>
-          </r>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Were stakeholders informed within communication SLAs? Was information accurate and complete? Did tone match incident severity? Were updates consistent across channels?"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Were stakeholders informed within communication SLAs? Was information accurate and complete? Did tone match incident severity? Were updates consistent across channels?"
 Reasoning: SLA assessment ensures process compliance; accuracy prevents loss of trust; tone alignment demonstrates professional judgment; consistency prevents confusion.</t>
-          </r>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Communications Lead / Customer Relations Director"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Communications Lead / Customer Relations Director"
 Reasoning: Communications team is accountable for message delivery; they understand audience expectations; they can improve templates and procedures.</t>
-          </r>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -2646,56 +2272,20 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Establish schedule to verify completion of action items and monitor for incident recurrence"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Establish schedule to verify completion of action items and monitor for incident recurrence"
 Reasoning: Scheduled follow-up ensures accountability; verification prevents items from slipping; monitoring catches early signs of recurrence.</t>
-          </r>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"When will action items be reviewed? What completion criteria define success? How will we verify the fix works in production? What metrics indicate recurrence?"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"When will action items be reviewed? What completion criteria define success? How will we verify the fix works in production? What metrics indicate recurrence?"
 Reasoning: Review schedule enforces deadlines; completion criteria ensure quality; production verification prevents regression; metrics provide early warning.</t>
-          </r>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-            </rPr>
-            <t>"Project Manager / Incident Commander"</t>
-          </r>
-          <r>
-            <rPr>
-              <i val="1"/>
-              <color rgb="00666666"/>
-            </rPr>
-            <t xml:space="preserve">
+          <t>"Project Manager / Incident Commander"
 Reasoning: Project Manager tracks deliverables; Incident Commander ensures organizational learning; both are accountable for closure.</t>
-          </r>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
